--- a/packages/cts1_mo_tools/src/cts1_mo_tools/cts1_spreadsheet_to_agenda/agenda_spreadsheet_template_example.xlsx
+++ b/packages/cts1_mo_tools/src/cts1_mo_tools/cts1_spreadsheet_to_agenda/agenda_spreadsheet_template_example.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meaga\OneDrive\Desktop\University\Clubs\CalgaryToSpace\Mission Operations\Software\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meaga\Programming\CalgaryToSpace\CTS-SAT-1-Ground-Station\packages\cts1_mo_tools\src\cts1_mo_tools\cts1_spreadsheet_to_agenda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBD49D4-1388-4965-81F7-79EB91234612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DC52CDE-6D9B-4B6D-8A59-456B2FAA9E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="36">
   <si>
     <t>Start UTC</t>
   </si>
@@ -39,12 +39,6 @@
     <t>Repeat</t>
   </si>
   <si>
-    <t>Window Start</t>
-  </si>
-  <si>
-    <t>Window End</t>
-  </si>
-  <si>
     <t>Interval</t>
   </si>
   <si>
@@ -81,9 +75,6 @@
     <t>tssent (UTC)</t>
   </si>
   <si>
-    <t>tsexec (UTC)</t>
-  </si>
-  <si>
     <t>resp_fname</t>
   </si>
   <si>
@@ -96,15 +87,9 @@
     <t>Random</t>
   </si>
   <si>
-    <t>CTS1+fs_read_text_file(adcs_data/{DATE}.run,0,0)!</t>
-  </si>
-  <si>
     <t>CTS1+adcs_get_current_state_1()!</t>
   </si>
   <si>
-    <t>adcs_data/{DATE}_state.run</t>
-  </si>
-  <si>
     <t>CTS1+adcs_set_run_mode(1)!</t>
   </si>
   <si>
@@ -123,9 +108,6 @@
     <t>CTS1+adcs_request_commissioning_telemetry(2,1,0)!</t>
   </si>
   <si>
-    <t>CTS1+fs_read_text_file(adcs_data/{DATE}_state.run,0,0)!</t>
-  </si>
-  <si>
     <t>adcs_data/2026-07-05.run</t>
   </si>
   <si>
@@ -139,6 +121,18 @@
   </si>
   <si>
     <t>TCMD Notes</t>
+  </si>
+  <si>
+    <t>tsexec Start (UTC)</t>
+  </si>
+  <si>
+    <t>tsexec End  (UTC)</t>
+  </si>
+  <si>
+    <t>CTS1+fs_read_text_file(adcs_data/2026-07-05.run,0,0)!</t>
+  </si>
+  <si>
+    <t>CTS1+fs_read_text_file(adcs_data/2026-07-05_state.run,0,0)!</t>
   </si>
 </sst>
 </file>
@@ -351,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -389,9 +383,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -404,9 +395,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -439,6 +427,15 @@
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -720,584 +717,568 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N23"/>
+  <dimension ref="B1:M23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="2"/>
     <col min="2" max="2" width="10.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="51.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="38.5546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.21875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="3"/>
-    <col min="9" max="9" width="12.77734375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="11.77734375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="20.88671875" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="2"/>
+    <col min="4" max="5" width="11.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="51.77734375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="38.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.21875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="3"/>
+    <col min="11" max="11" width="20.88671875" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="29"/>
-    </row>
-    <row r="3" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="27"/>
+    </row>
+    <row r="3" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="26"/>
+      <c r="C3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="28"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="24"/>
+      <c r="L3"/>
       <c r="M3"/>
-      <c r="N3"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="23"/>
-      <c r="N4"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C4" s="19"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="21"/>
+      <c r="M4"/>
+    </row>
+    <row r="5" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="13">
+        <v>0</v>
+      </c>
+      <c r="E6" s="13">
+        <v>0</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="16"/>
+      <c r="I6" s="13">
+        <v>5</v>
+      </c>
+      <c r="J6" s="13">
+        <v>10</v>
+      </c>
+      <c r="K6" s="15"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="17">
+        <v>0.30138888888888887</v>
+      </c>
+      <c r="D7" s="17">
+        <v>0.30138888888888887</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="16"/>
+      <c r="I7" s="13">
+        <v>3</v>
+      </c>
+      <c r="J7" s="13">
+        <v>3</v>
+      </c>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="17">
+        <v>0.30150462962962965</v>
+      </c>
+      <c r="D8" s="17">
+        <v>0.30150462962962965</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="16"/>
+      <c r="I8" s="13">
+        <v>3</v>
+      </c>
+      <c r="J8" s="13">
+        <v>3</v>
+      </c>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="17">
+        <v>0.30277777777777776</v>
+      </c>
+      <c r="D9" s="17">
+        <v>0.30277777777777776</v>
+      </c>
+      <c r="E9" s="17"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="13">
+        <v>3</v>
+      </c>
+      <c r="J9" s="13">
+        <v>3</v>
+      </c>
+      <c r="K9" s="15"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="17">
+        <v>0.30289351851851853</v>
+      </c>
+      <c r="D10" s="17">
+        <v>0.30289351851851853</v>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="13">
+        <v>3</v>
+      </c>
+      <c r="J10" s="13">
+        <v>3</v>
+      </c>
+      <c r="K10" s="15"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="17">
+        <v>0.30300925925925926</v>
+      </c>
+      <c r="D11" s="17">
+        <v>0.30300925925925926</v>
+      </c>
+      <c r="E11" s="17"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="H11" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="13">
+        <v>3</v>
+      </c>
+      <c r="J11" s="13">
+        <v>3</v>
+      </c>
+      <c r="K11" s="15"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="17">
+        <v>0.30312499999999998</v>
+      </c>
+      <c r="D12" s="17">
+        <v>0.30312499999999998</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="13">
+        <v>3</v>
+      </c>
+      <c r="J12" s="13">
+        <v>3</v>
+      </c>
+      <c r="K12" s="15"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="17">
+        <v>0.30324074074074076</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0.30324074074074076</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="H13" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="13">
+        <v>3</v>
+      </c>
+      <c r="J13" s="13">
+        <v>3</v>
+      </c>
+      <c r="K13" s="15"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="17">
+        <v>0.30335648148148148</v>
+      </c>
+      <c r="D14" s="17">
+        <v>0.30335648148148148</v>
+      </c>
+      <c r="E14" s="17"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="13">
+        <v>3</v>
+      </c>
+      <c r="J14" s="13">
+        <v>3</v>
+      </c>
+      <c r="K14" s="15"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="17">
+        <v>0.3034722222222222</v>
+      </c>
+      <c r="D15" s="17">
+        <v>0.3034722222222222</v>
+      </c>
+      <c r="E15" s="17"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="13">
+        <v>3</v>
+      </c>
+      <c r="J15" s="13">
+        <v>3</v>
+      </c>
+      <c r="K15" s="15"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="17">
+        <v>0.30358796296296298</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0.30358796296296298</v>
+      </c>
+      <c r="E16" s="17"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="13">
+        <v>3</v>
+      </c>
+      <c r="J16" s="13">
+        <v>3</v>
+      </c>
+      <c r="K16" s="15"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="17">
+        <v>0.3037037037037037</v>
+      </c>
+      <c r="D17" s="17">
+        <v>0.3037037037037037</v>
+      </c>
+      <c r="E17" s="17"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="13">
+        <v>3</v>
+      </c>
+      <c r="J17" s="13">
+        <v>3</v>
+      </c>
+      <c r="K17" s="15"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="17">
+        <v>0.30381944444444442</v>
+      </c>
+      <c r="D18" s="17">
+        <v>0.30381944444444442</v>
+      </c>
+      <c r="E18" s="17"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="13">
+        <v>3</v>
+      </c>
+      <c r="J18" s="13">
+        <v>3</v>
+      </c>
+      <c r="K18" s="15"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="17">
+        <v>0.30729166666666669</v>
+      </c>
+      <c r="D19" s="17">
+        <v>0.30729166666666669</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="13">
+        <v>3</v>
+      </c>
+      <c r="J19" s="13">
+        <v>3</v>
+      </c>
+      <c r="K19" s="15"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B20" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="14">
-        <v>0</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="14">
-        <v>5</v>
-      </c>
-      <c r="H6" s="14">
+      <c r="C20" s="17">
+        <v>0.34375</v>
+      </c>
+      <c r="D20" s="17">
+        <v>0.34375</v>
+      </c>
+      <c r="E20" s="17">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="16"/>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="19">
-        <v>0.30138888888888887</v>
-      </c>
-      <c r="D7" s="19">
-        <v>0.30138888888888887</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="G20" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="14">
-        <v>3</v>
-      </c>
-      <c r="H7" s="14">
-        <v>3</v>
-      </c>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="16"/>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="19">
-        <v>0.30150462962962965</v>
-      </c>
-      <c r="D8" s="19">
-        <v>0.30150462962962965</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="14">
-        <v>3</v>
-      </c>
-      <c r="H8" s="14">
-        <v>3</v>
-      </c>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="16"/>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="19">
-        <v>0.30277777777777776</v>
-      </c>
-      <c r="D9" s="19">
-        <v>0.30277777777777776</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="14">
-        <v>3</v>
-      </c>
-      <c r="H9" s="14">
-        <v>3</v>
-      </c>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="16"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="19">
-        <v>0.30289351851851853</v>
-      </c>
-      <c r="D10" s="19">
-        <v>0.30289351851851853</v>
-      </c>
-      <c r="E10" s="17" t="s">
+      <c r="H20" s="16"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="15"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="17">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="D21" s="17">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="E21" s="17">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="14">
-        <v>3</v>
-      </c>
-      <c r="H10" s="14">
-        <v>3</v>
-      </c>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="16"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="19">
-        <v>0.30300925925925926</v>
-      </c>
-      <c r="D11" s="19">
-        <v>0.30300925925925926</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="17" t="s">
+      <c r="H21" s="16"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="15"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B22" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="17">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D22" s="17">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="E22" s="17">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="14">
-        <v>3</v>
-      </c>
-      <c r="H11" s="14">
-        <v>3</v>
-      </c>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="16"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="19">
-        <v>0.30312499999999998</v>
-      </c>
-      <c r="D12" s="19">
-        <v>0.30312499999999998</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="14">
-        <v>3</v>
-      </c>
-      <c r="H12" s="14">
-        <v>3</v>
-      </c>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="16"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="19">
-        <v>0.30324074074074076</v>
-      </c>
-      <c r="D13" s="19">
-        <v>0.30324074074074076</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="14">
-        <v>3</v>
-      </c>
-      <c r="H13" s="14">
-        <v>3</v>
-      </c>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="16"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B14" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="19">
-        <v>0.30335648148148148</v>
-      </c>
-      <c r="D14" s="19">
-        <v>0.30335648148148148</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="14">
-        <v>3</v>
-      </c>
-      <c r="H14" s="14">
-        <v>3</v>
-      </c>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="16"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="19">
-        <v>0.3034722222222222</v>
-      </c>
-      <c r="D15" s="19">
-        <v>0.3034722222222222</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="14">
-        <v>3</v>
-      </c>
-      <c r="H15" s="14">
-        <v>3</v>
-      </c>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="16"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="19">
-        <v>0.30358796296296298</v>
-      </c>
-      <c r="D16" s="19">
-        <v>0.30358796296296298</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="14">
-        <v>3</v>
-      </c>
-      <c r="H16" s="14">
-        <v>3</v>
-      </c>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="16"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="19">
-        <v>0.3037037037037037</v>
-      </c>
-      <c r="D17" s="19">
-        <v>0.3037037037037037</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="14">
-        <v>3</v>
-      </c>
-      <c r="H17" s="14">
-        <v>3</v>
-      </c>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="16"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="19">
-        <v>0.30381944444444442</v>
-      </c>
-      <c r="D18" s="19">
-        <v>0.30381944444444442</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="14">
-        <v>3</v>
-      </c>
-      <c r="H18" s="14">
-        <v>3</v>
-      </c>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="16"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="19">
-        <v>0.30729166666666669</v>
-      </c>
-      <c r="D19" s="19">
-        <v>0.30729166666666669</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" s="14">
-        <v>3</v>
-      </c>
-      <c r="H19" s="14">
-        <v>3</v>
-      </c>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="16"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="18">
-        <v>0.34375</v>
-      </c>
-      <c r="J20" s="18">
-        <v>0.34722222222222221</v>
-      </c>
-      <c r="K20" s="14" t="s">
+      <c r="H22" s="16"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="15"/>
+    </row>
+    <row r="23" spans="2:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="30">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D23" s="30">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E23" s="30">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="L20" s="16"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="18">
-        <v>0.34722222222222221</v>
-      </c>
-      <c r="J21" s="18">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="L21" s="16"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="17"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="18">
-        <v>0.40972222222222221</v>
-      </c>
-      <c r="J22" s="18">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="L22" s="16"/>
-    </row>
-    <row r="23" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J23" s="13">
-        <v>0.4201388888888889</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L23" s="20"/>
+      <c r="G23" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" s="12"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="C3:L3"/>
-    <mergeCell ref="C2:L2"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="C2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
